--- a/output/pdf_financials_xlsx/PML.xlsx
+++ b/output/pdf_financials_xlsx/PML.xlsx
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.719459</v>
+        <v>-2.480073</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1.066264</v>
@@ -1312,28 +1312,28 @@
         <v>2.05812</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.472248</v>
+        <v>-3.472248</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.304456</v>
+        <v>-5.304456</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.261658</v>
+        <v>-3.261658</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.18619</v>
+        <v>-3.18619</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.617102</v>
+        <v>-4.617102</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.531015</v>
+        <v>-2.531015</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.505061</v>
+        <v>-0.505061</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.542933</v>
+        <v>-4.542933</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>5.181476</v>
@@ -1370,7 +1370,7 @@
         <v>0.213432</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.111315</v>
+        <v>-4.227555</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1397,7 +1397,7 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-10.362952</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0.851648</v>
@@ -1619,43 +1619,43 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.599766</v>
+        <v>-2.599766</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.852832</v>
+        <v>-0.852832</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.169435</v>
+        <v>-2.169435</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.472248</v>
+        <v>-3.472248</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5.304456</v>
+        <v>-5.304456</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.261658</v>
+        <v>-3.261658</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.18619</v>
+        <v>-3.18619</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.617102</v>
+        <v>-4.617102</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.531015</v>
+        <v>-2.531015</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.505061</v>
+        <v>-0.505061</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.542933</v>
+        <v>-4.542933</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>5.181476</v>
+        <v>-5.181476</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.083125</v>
+        <v>-1.083125</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-8.229915</v>
@@ -1802,43 +1802,43 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.599766</v>
+        <v>-2.599766</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.852832</v>
+        <v>-0.852832</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.169435</v>
+        <v>-2.169435</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.472248</v>
+        <v>-3.472248</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.304456</v>
+        <v>-5.304456</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.261658</v>
+        <v>-3.261658</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.18619</v>
+        <v>-3.18619</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.617102</v>
+        <v>-4.617102</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.531015</v>
+        <v>-2.531015</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.505061</v>
+        <v>-0.505061</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.542933</v>
+        <v>-4.542933</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5.181476</v>
+        <v>-5.181476</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.083125</v>
+        <v>-1.083125</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-8.229915</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>86.658867</v>
+        <v>-86.658867</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.719459</v>
+        <v>-2.480073</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>1.066264</v>
@@ -2141,28 +2141,28 @@
         <v>2.05812</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.472248</v>
+        <v>-3.472248</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.304456</v>
+        <v>-5.304456</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.261658</v>
+        <v>-3.261658</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.18619</v>
+        <v>-3.18619</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.617102</v>
+        <v>-4.617102</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.531015</v>
+        <v>-2.531015</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.505061</v>
+        <v>-0.505061</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4.542933</v>
+        <v>-4.542933</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>5.181476</v>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.719459</v>
+        <v>-2.480073</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>1.066264</v>
@@ -2263,28 +2263,28 @@
         <v>2.05812</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.472248</v>
+        <v>-3.472248</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.304456</v>
+        <v>-5.304456</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.261658</v>
+        <v>-3.261658</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.18619</v>
+        <v>-3.18619</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.617102</v>
+        <v>-4.617102</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.531015</v>
+        <v>-2.531015</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.505061</v>
+        <v>-0.505061</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4.542933</v>
+        <v>-4.542933</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>5.181476</v>
@@ -2412,40 +2412,40 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>4.401353357414103</v>
+        <v>-4.826188583965068</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>20.01680634439501</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>5.408576759372631</v>
+        <v>205.4085767593727</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>367.9190589129806</v>
@@ -6621,10 +6621,10 @@
         <v>-2.252063</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>3.472248</v>
+        <v>-3.472248</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>5.304456</v>
+        <v>-5.304456</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-3.261658</v>
@@ -7821,46 +7821,46 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-14.688373</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-10.999465</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-7.246316</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-5.178886</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-2.431383</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-5.247575</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-4.762034</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-3.068267</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-2.797996</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.646255</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-3.440242</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-4.441188</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-2.026579</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-1.85437</v>
       </c>
     </row>
     <row r="119">
@@ -29878,7 +29878,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32816,7 +32820,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -37090,7 +37098,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -41296,7 +41308,11 @@
           <t>Exploration and evaluation expenditures (Note 6)</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -43514,7 +43530,11 @@
           <t>Exploration and evaluation expenditures (Note 5)</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -50872,7 +50892,11 @@
           <t>Exploration and evaluation expenditures (note 5)</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -54142,7 +54166,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -74606,7 +74634,7 @@
         </is>
       </c>
       <c r="Q627" s="5" t="n">
-        <v>1.083125</v>
+        <v>-1.083125</v>
       </c>
       <c r="R627" s="5" t="n">
         <v>-8.229915</v>
@@ -77034,10 +77062,10 @@
         </is>
       </c>
       <c r="Q650" s="5" t="n">
-        <v>1.082492</v>
+        <v>-1.082492</v>
       </c>
       <c r="R650" s="5" t="n">
-        <v>8.230314999999999</v>
+        <v>-8.230314999999999</v>
       </c>
       <c r="S650" t="inlineStr">
         <is>
@@ -80383,10 +80411,10 @@
         </is>
       </c>
       <c r="P683" s="5" t="n">
-        <v>5.181476</v>
+        <v>-5.181476</v>
       </c>
       <c r="Q683" s="5" t="n">
-        <v>1.083125</v>
+        <v>-1.083125</v>
       </c>
       <c r="R683" t="inlineStr">
         <is>
@@ -80575,13 +80603,13 @@
         </is>
       </c>
       <c r="L685" s="5" t="n">
-        <v>4.625102</v>
+        <v>-4.625102</v>
       </c>
       <c r="M685" s="5" t="n">
-        <v>2.527015</v>
+        <v>-2.527015</v>
       </c>
       <c r="N685" s="5" t="n">
-        <v>0.509561</v>
+        <v>-0.509561</v>
       </c>
       <c r="O685" t="inlineStr">
         <is>
@@ -80589,10 +80617,10 @@
         </is>
       </c>
       <c r="P685" s="5" t="n">
-        <v>5.182843</v>
+        <v>-5.182843</v>
       </c>
       <c r="Q685" s="5" t="n">
-        <v>1.082492</v>
+        <v>-1.082492</v>
       </c>
       <c r="R685" t="inlineStr">
         <is>
@@ -82527,37 +82555,37 @@
         </is>
       </c>
       <c r="F704" s="5" t="n">
-        <v>0.852832</v>
+        <v>-0.852832</v>
       </c>
       <c r="G704" s="5" t="n">
-        <v>2.169435</v>
+        <v>-2.169435</v>
       </c>
       <c r="H704" s="5" t="n">
-        <v>3.472248</v>
+        <v>-3.472248</v>
       </c>
       <c r="I704" s="5" t="n">
-        <v>5.304456</v>
+        <v>-5.304456</v>
       </c>
       <c r="J704" s="5" t="n">
-        <v>3.261658</v>
+        <v>-3.261658</v>
       </c>
       <c r="K704" s="5" t="n">
-        <v>3.18619</v>
+        <v>-3.18619</v>
       </c>
       <c r="L704" s="5" t="n">
-        <v>4.617102</v>
+        <v>-4.617102</v>
       </c>
       <c r="M704" s="5" t="n">
-        <v>2.531015</v>
+        <v>-2.531015</v>
       </c>
       <c r="N704" s="5" t="n">
-        <v>0.505061</v>
+        <v>-0.505061</v>
       </c>
       <c r="O704" s="5" t="n">
-        <v>4.542933</v>
+        <v>-4.542933</v>
       </c>
       <c r="P704" s="5" t="n">
-        <v>5.181476</v>
+        <v>-5.181476</v>
       </c>
       <c r="Q704" t="inlineStr">
         <is>
@@ -82761,13 +82789,13 @@
         </is>
       </c>
       <c r="N706" s="5" t="n">
-        <v>0.509561</v>
+        <v>-0.509561</v>
       </c>
       <c r="O706" s="5" t="n">
-        <v>4.5431</v>
+        <v>-4.5431</v>
       </c>
       <c r="P706" s="5" t="n">
-        <v>5.182843</v>
+        <v>-5.182843</v>
       </c>
       <c r="Q706" t="inlineStr">
         <is>
@@ -86064,10 +86092,10 @@
         </is>
       </c>
       <c r="K738" s="5" t="n">
-        <v>3.18619</v>
+        <v>-3.18619</v>
       </c>
       <c r="L738" s="5" t="n">
-        <v>4.617102</v>
+        <v>-4.617102</v>
       </c>
       <c r="M738" t="inlineStr">
         <is>
@@ -86488,10 +86516,10 @@
         </is>
       </c>
       <c r="K742" s="5" t="n">
-        <v>3.15419</v>
+        <v>-3.15419</v>
       </c>
       <c r="L742" s="5" t="n">
-        <v>4.625102</v>
+        <v>-4.625102</v>
       </c>
       <c r="M742" t="inlineStr">
         <is>
@@ -87929,10 +87957,10 @@
         </is>
       </c>
       <c r="J756" s="5" t="n">
-        <v>3.295658</v>
+        <v>-3.295658</v>
       </c>
       <c r="K756" s="5" t="n">
-        <v>3.15419</v>
+        <v>-3.15419</v>
       </c>
       <c r="L756" t="inlineStr">
         <is>
@@ -88651,13 +88679,13 @@
         </is>
       </c>
       <c r="H763" s="5" t="n">
-        <v>3.444248</v>
+        <v>-3.444248</v>
       </c>
       <c r="I763" s="5" t="n">
-        <v>5.346456</v>
+        <v>-5.346456</v>
       </c>
       <c r="J763" s="5" t="n">
-        <v>3.295658</v>
+        <v>-3.295658</v>
       </c>
       <c r="K763" t="inlineStr">
         <is>
@@ -90426,10 +90454,10 @@
         </is>
       </c>
       <c r="G780" s="5" t="n">
-        <v>1.83176</v>
+        <v>-1.83176</v>
       </c>
       <c r="H780" s="5" t="n">
-        <v>3.444248</v>
+        <v>-3.444248</v>
       </c>
       <c r="I780" t="inlineStr">
         <is>
@@ -92418,10 +92446,10 @@
         </is>
       </c>
       <c r="E799" s="5" t="n">
-        <v>2.599766</v>
+        <v>-2.599766</v>
       </c>
       <c r="F799" s="5" t="n">
-        <v>0.852832</v>
+        <v>-0.852832</v>
       </c>
       <c r="G799" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PML.xlsx
+++ b/output/pdf_financials_xlsx/PML.xlsx
@@ -1059,58 +1059,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.154944</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002907</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007113</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057494</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.135279</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.168315</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.090797</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.042142</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008014</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021386</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01317</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009593000000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.083466</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.07739</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.034515</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.239372</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.037874</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.003557</v>
       </c>
     </row>
     <row r="13">
@@ -2132,58 +2132,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.480073</v>
+        <v>-2.325129</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.066264</v>
+        <v>1.069171</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.05812</v>
+        <v>2.065233</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.472248</v>
+        <v>-3.414754</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.304456</v>
+        <v>-5.169177</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.261658</v>
+        <v>-3.093343</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.18619</v>
+        <v>-3.095393</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.617102</v>
+        <v>-4.57496</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.531015</v>
+        <v>-2.523001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.505061</v>
+        <v>-0.483675</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.542933</v>
+        <v>-4.529763</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>5.181476</v>
+        <v>5.191069</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.231477</v>
+        <v>0.314943</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-8.660468</v>
+        <v>-8.737857999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.384513</v>
+        <v>-0.419028</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.094033</v>
+        <v>-2.333405</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.201458</v>
+        <v>-1.239332</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-2.545299</v>
+        <v>-2.548856</v>
       </c>
     </row>
     <row r="28">
@@ -2254,58 +2254,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.480073</v>
+        <v>-2.325129</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.066264</v>
+        <v>1.069171</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.05812</v>
+        <v>2.065233</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.472248</v>
+        <v>-3.414754</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.304456</v>
+        <v>-5.169177</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.261658</v>
+        <v>-3.093343</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.18619</v>
+        <v>-3.095393</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.617102</v>
+        <v>-4.57496</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.531015</v>
+        <v>-2.523001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.505061</v>
+        <v>-0.483675</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.542933</v>
+        <v>-4.529763</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>5.181476</v>
+        <v>5.191069</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.231477</v>
+        <v>0.314943</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-8.660468</v>
+        <v>-8.737857999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.384513</v>
+        <v>-0.419028</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.094033</v>
+        <v>-2.333405</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.201458</v>
+        <v>-1.239332</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-2.545299</v>
+        <v>-2.548856</v>
       </c>
     </row>
     <row r="30">
@@ -60658,7 +60658,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -60762,7 +60762,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -73092,7 +73092,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -73198,7 +73198,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -76144,7 +76144,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -79180,7 +79180,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -79288,7 +79288,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -81928,7 +81928,7 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
@@ -82038,7 +82038,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E699" s="5" t="n">

--- a/output/pdf_financials_xlsx/PML.xlsx
+++ b/output/pdf_financials_xlsx/PML.xlsx
@@ -7467,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.01607</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -39412,7 +39412,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -41728,7 +41732,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PML.xlsx
+++ b/output/pdf_financials_xlsx/PML.xlsx
@@ -763,49 +763,49 @@
         <v>0.282113</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.503094</v>
+        <v>0.547427</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.919566</v>
+        <v>1.024066</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5763819999999999</v>
+        <v>0.673382</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.501849</v>
+        <v>0.590224</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.164248</v>
+        <v>0.240565</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.131623</v>
+        <v>0.192834</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.132217</v>
+        <v>0.319149</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.08845600000000001</v>
+        <v>0.284199</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.080053</v>
+        <v>0.27946</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.037163</v>
+        <v>0.112276</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.356447</v>
+        <v>0.406569</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.235375</v>
+        <v>0.297288</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.011875</v>
+        <v>0.128889</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.01766</v>
+        <v>0.133836</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.010088</v>
+        <v>0.124484</v>
       </c>
     </row>
     <row r="8">
@@ -976,19 +976,19 @@
         <v>1.368215</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.739317</v>
+        <v>1.789439</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.18286</v>
+        <v>1.244773</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.788567</v>
+        <v>0.905581</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.715415</v>
+        <v>0.831591</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.984191</v>
+        <v>1.098587</v>
       </c>
     </row>
     <row r="11">
@@ -1037,19 +1037,19 @@
         <v>-1.368215</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1.739317</v>
+        <v>-1.789439</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.18286</v>
+        <v>-1.244773</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.788567</v>
+        <v>-0.905581</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.715415</v>
+        <v>-0.831591</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.984191</v>
+        <v>-1.098587</v>
       </c>
     </row>
     <row r="12">
@@ -1370,7 +1370,7 @@
         <v>0.213432</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-4.227555</v>
+        <v>-0.193943</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1403,7 +1403,7 @@
         <v>-0.851648</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.430553</v>
+        <v>-0.430553</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.376746</v>
@@ -2418,7 +2418,7 @@
         <v>20.01680634439501</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>205.4085767593727</v>
+        <v>9.423308650613182</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -7371,19 +7371,19 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001576</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.08980200000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.198815</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.030447</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.064524</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -7392,28 +7392,28 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003261</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008669</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005253</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000655</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01328</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016392</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.059263</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019268</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -7623,13 +7623,13 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.049858</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.114671</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>3.504376</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -8870,19 +8870,19 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001576</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.08980200000000001</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.198815</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.030447</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.064524</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8891,28 +8891,28 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003261</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008669</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005253</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000655</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01328</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016392</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.059263</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019268</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-2.332383</v>
+        <v>-2.396907</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-2.574401</v>
@@ -8962,28 +8962,28 @@
         <v>-2.058287</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-2.193305</v>
+        <v>-2.196566</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-2.584381</v>
+        <v>-2.59305</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-3.085644</v>
+        <v>-3.090897</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.127816</v>
+        <v>-2.128471</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.10848</v>
+        <v>-1.12176</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.283265</v>
+        <v>-1.299657</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.848734</v>
+        <v>-1.907997</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-2.21958</v>
+        <v>-2.238848</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>-1.45814</v>
@@ -30512,7 +30512,11 @@
           <t>Gross proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -32922,7 +32926,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -35008,7 +35016,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -35218,7 +35230,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -36468,7 +36484,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -39522,7 +39542,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -40898,7 +40922,11 @@
           <t>Deferred income tax expense (Note 11)</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -54388,7 +54416,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -55314,7 +55346,11 @@
           <t>Proceeds from short-term investment</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -56056,7 +56092,11 @@
           <t>Proceeds from short-term investment (note 4)</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -56268,7 +56308,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -56802,7 +56846,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -57750,7 +57798,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -57958,7 +58010,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -59236,7 +59292,11 @@
           <t>Agents warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -60042,7 +60102,11 @@
           <t>Directors’ fees 14</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -63090,7 +63154,11 @@
           <t>Directors’ fees 12</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
@@ -70782,7 +70850,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -72466,7 +72538,11 @@
           <t>Directors’ fees 12</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>
@@ -74472,7 +74548,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
@@ -75942,7 +76022,11 @@
           <t>Directors’ fees 12, 16</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E640" t="inlineStr">
         <is>
           <t>-</t>
@@ -78138,7 +78222,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E661" t="inlineStr">
         <is>
           <t>-</t>
@@ -88254,7 +88342,11 @@
           <t>Director’s fees</t>
         </is>
       </c>
-      <c r="D759" t="inlineStr"/>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E759" t="inlineStr">
         <is>
           <t>-</t>
@@ -91292,7 +91384,11 @@
           <t>Future income tax recovery (note 8)</t>
         </is>
       </c>
-      <c r="D788" t="inlineStr"/>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E788" t="inlineStr">
         <is>
           <t>-</t>
